--- a/tests/fixtures/calce/CS2_TEST/CS2_TEST_session1.xlsx
+++ b/tests/fixtures/calce/CS2_TEST/CS2_TEST_session1.xlsx
@@ -773,10 +773,10 @@
         <v>4.2</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1.111</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="I12" t="n">
         <v>25.2</v>
@@ -802,10 +802,10 @@
         <v>4.140000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1223222222222222</v>
+        <v>1.233322222222222</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1211111111111111</v>
+        <v>1.221111111111111</v>
       </c>
       <c r="I13" t="n">
         <v>25.2</v>
@@ -831,10 +831,10 @@
         <v>4.08</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2446444444444444</v>
+        <v>1.355644444444445</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2422222222222222</v>
+        <v>1.342222222222222</v>
       </c>
       <c r="I14" t="n">
         <v>25.2</v>
@@ -860,10 +860,10 @@
         <v>4.02</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3669666666666667</v>
+        <v>1.477966666666667</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3633333333333333</v>
+        <v>1.463333333333333</v>
       </c>
       <c r="I15" t="n">
         <v>25.2</v>
@@ -889,10 +889,10 @@
         <v>3.96</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4892888888888889</v>
+        <v>1.600288888888889</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4844444444444445</v>
+        <v>1.584444444444445</v>
       </c>
       <c r="I16" t="n">
         <v>25.2</v>
@@ -918,10 +918,10 @@
         <v>3.9</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6116111111111112</v>
+        <v>1.722611111111111</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6055555555555556</v>
+        <v>1.705555555555556</v>
       </c>
       <c r="I17" t="n">
         <v>25.2</v>
@@ -947,10 +947,10 @@
         <v>3.84</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7339333333333333</v>
+        <v>1.844933333333333</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7266666666666667</v>
+        <v>1.826666666666667</v>
       </c>
       <c r="I18" t="n">
         <v>25.2</v>
@@ -976,10 +976,10 @@
         <v>3.78</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8562555555555555</v>
+        <v>1.967255555555556</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8477777777777777</v>
+        <v>1.947777777777778</v>
       </c>
       <c r="I19" t="n">
         <v>25.2</v>
@@ -1005,10 +1005,10 @@
         <v>3.72</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9785777777777778</v>
+        <v>2.089577777777778</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9688888888888889</v>
+        <v>2.068888888888889</v>
       </c>
       <c r="I20" t="n">
         <v>25.2</v>
@@ -1034,10 +1034,10 @@
         <v>3.66</v>
       </c>
       <c r="G21" t="n">
-        <v>1.1009</v>
+        <v>2.2119</v>
       </c>
       <c r="H21" t="n">
-        <v>1.09</v>
+        <v>2.19</v>
       </c>
       <c r="I21" t="n">
         <v>25.2</v>
